--- a/docs/Final_Project_UI_Bug_Siyahisi.xlsx
+++ b/docs/Final_Project_UI_Bug_Siyahisi.xlsx
@@ -864,7 +864,7 @@
     <t xml:space="preserve">Avtomatlaşdırma</t>
   </si>
   <si>
-    <t xml:space="preserve">65 Selenium ssenarisi: 43 sabit, 22 məlum bug (known-bug) ssenarisi</t>
+    <t xml:space="preserve">97 Selenium ssenarisi: 75 sabit (hamısı keçir), 22 məlum bug (known-bug) ssenarisi</t>
   </si>
   <si>
     <t xml:space="preserve">Screenshot</t>
@@ -1153,9 +1153,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>183240</xdr:colOff>
+      <xdr:colOff>182880</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>17640</xdr:rowOff>
+      <xdr:rowOff>17280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1169,7 +1169,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="571680"/>
-          <a:ext cx="10476000" cy="6303960"/>
+          <a:ext cx="10475640" cy="6303600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1190,9 +1190,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>183240</xdr:colOff>
+      <xdr:colOff>182880</xdr:colOff>
       <xdr:row>73</xdr:row>
-      <xdr:rowOff>17640</xdr:rowOff>
+      <xdr:rowOff>17280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1206,7 +1206,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="7620120"/>
-          <a:ext cx="10476000" cy="6303960"/>
+          <a:ext cx="10475640" cy="6303600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/docs/Final_Project_UI_Bug_Siyahisi.xlsx
+++ b/docs/Final_Project_UI_Bug_Siyahisi.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="308">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -831,6 +831,113 @@
     <t xml:space="preserve">Selenium diaqnostikasında müşahidə olunub; əl ilə sildikdə də təkrarlanıb-təkrarlanmadığı yoxlanmalıdır</t>
   </si>
   <si>
+    <t xml:space="preserve">BUG-024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Məbləğ sahəsi maksimum limiti (80 000) yoxlamır</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. /az açın
+2. Kalkulyatorda məbləğ sahəsinə 99999999 yazın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limit xətası və ya dəyərin 80 000-ə məhdudlaşdırılması</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sahə 99999999 qəbul edir, slayder 80000-də qalır (sinxron deyil), cəmi 101 822 141.21 AZN göstərilir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brauzerdə əl ilə təsdiqləndi (UI-CAL-018)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUG-025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ana səhifə</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konsolda resurs və CORS xətaları</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. /az açın
+2. Brauzer konsoluna baxın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xəta yoxdur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORS (infobank.az), 404, 400, ERR_TOO_MANY_REDIRECTS və timeout xətaları</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bəzi timeout-lar test mühitindən ola bilər (UI-HOM-005)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUG-026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Əmanətlər</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Əmanət kalkulyatoru minimum məbləğdən (100) az dəyəri qəbul edir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. /az/emanetler/digital-depozit açın
+2. Məbləğ sahəsinə 99 yazın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xəta mesajı və ya rədd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99 qəbul edilir, 99.60 AZN cəmi göstərilir, xəta yoxdur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brauzerdə əl ilə təsdiqləndi (UI-DEP-018)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OBS-015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kampaniyalar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaxtı bitmiş müsabiqə hələ də siyahıdadır</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. /az/kampaniyalar açın
+2. "İstanbula 2 nəfərlik bilet" kampaniyasına baxın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bitmiş kampaniya aktiv kimi görünmür</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Müsabiqə 17–27 iyul 2026 üçün idi, oktyabrda hələ siyahıdadır</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biznes ilə dəqiqləşdirmək (UI-CMP-002)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OBS-016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEO və dillər</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/en və /ru səhifələrində html lang="az", başlıq AZ; daxili səhifələrdə canonical /az-a işarə edir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. /en və /ru açın, html lang və title-a baxın
+2. /az/kartlar/debet canonical-a baxın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lang="en"/"ru", müvafiq başlıq; canonical öz URL-ni göstərir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lang="az" və AZ başlıq; canonical https://www.bankofbaku.com/az; /az/biznes başlığı ana səhifə başlığıdır</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI-LNG-003, 004, ERR-002, BIZ-002</t>
+  </si>
+  <si>
     <t xml:space="preserve">Say</t>
   </si>
   <si>
@@ -852,13 +959,13 @@
     <t xml:space="preserve">Qalan yoxlamalar</t>
   </si>
   <si>
-    <t xml:space="preserve">Rəng kontrastı, klaviatura fokusu, yüklənmə müddəti, valyuta (USD/EUR) əmanət hesablaması, FAQ akkordeonu</t>
+    <t xml:space="preserve">Qalan 21 case: hücum xarakterli (ERR-003, SRC-004, SEC-005), offline (ERR-004), kontrast/fokus (A11-002, 005), performans (PRF-001), dil qaydaları (LNG-005…012), NAV-013, HOM-002, CAL-017, 019, 020, CHT-004</t>
   </si>
   <si>
     <t xml:space="preserve">Bug-ların biznesə təqdimi</t>
   </si>
   <si>
-    <t xml:space="preserve">BUG-017 – 023 və OBS-006 – 014 üçün biznes təsdiqi lazımdır</t>
+    <t xml:space="preserve">BUG-017 – 026 və OBS-006 – 016 üçün biznes təsdiqi lazımdır</t>
   </si>
   <si>
     <t xml:space="preserve">Avtomatlaşdırma</t>
@@ -1153,9 +1260,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>182880</xdr:colOff>
+      <xdr:colOff>182160</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>17280</xdr:rowOff>
+      <xdr:rowOff>16560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1169,7 +1276,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="571680"/>
-          <a:ext cx="10475640" cy="6303600"/>
+          <a:ext cx="10474920" cy="6302880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1190,9 +1297,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>182880</xdr:colOff>
+      <xdr:colOff>182160</xdr:colOff>
       <xdr:row>73</xdr:row>
-      <xdr:rowOff>17280</xdr:rowOff>
+      <xdr:rowOff>16560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1206,7 +1313,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="7620120"/>
-          <a:ext cx="10475640" cy="6303600"/>
+          <a:ext cx="10474920" cy="6302880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1401,7 +1508,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10"/>
@@ -2515,6 +2622,151 @@
       </c>
       <c r="I38" s="3" t="s">
         <v>256</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -2556,7 +2808,7 @@
         <v>6</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>257</v>
+        <v>291</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2574,7 +2826,7 @@
       </c>
       <c r="B3" s="5" t="n">
         <f aca="false">COUNTIFS('Bug siyahısı'!G2:G200,A3,'Bug siyahısı'!H2:H200,"&lt;&gt;Rədd edildi")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2583,16 +2835,16 @@
       </c>
       <c r="B4" s="5" t="n">
         <f aca="false">COUNTIFS('Bug siyahısı'!G2:G200,A4,'Bug siyahısı'!H2:H200,"&lt;&gt;Rədd edildi")</f>
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>258</v>
+        <v>292</v>
       </c>
       <c r="B5" s="6" t="n">
         <f aca="false">SUM(B2:B4)</f>
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -2621,10 +2873,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>259</v>
+        <v>293</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>260</v>
+        <v>294</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>8</v>
@@ -2635,10 +2887,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>261</v>
+        <v>295</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>262</v>
+        <v>296</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2646,10 +2898,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>263</v>
+        <v>297</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>264</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2657,10 +2909,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>266</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2668,10 +2920,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>268</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2679,10 +2931,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>269</v>
+        <v>303</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
     </row>
   </sheetData>
@@ -2711,17 +2963,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>271</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>272</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>273</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Final_Project_UI_Bug_Siyahisi.xlsx
+++ b/docs/Final_Project_UI_Bug_Siyahisi.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="231">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -140,10 +140,7 @@
     <t xml:space="preserve">Müddət: "Kredit müddəti düzgün qeyd olunmayıb". Məbləğ: heç bir mesaj yoxdur</t>
   </si>
   <si>
-    <t xml:space="preserve">Yeni</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUG-003 ilə əlaqəlidir</t>
+    <t xml:space="preserve">Brauzerdə əl ilə yenidən təsdiqləndi (12.10.2026)</t>
   </si>
   <si>
     <t xml:space="preserve">BUG-005</t>
@@ -180,9 +177,6 @@
   </si>
   <si>
     <t xml:space="preserve">Qəbul olunur: 88.38 / 1060.60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biznes qaydasını dəqiqləşdirmək lazımdır</t>
   </si>
   <si>
     <t xml:space="preserve">BUG-007</t>
@@ -286,32 +280,6 @@
     <t xml:space="preserve">Real Chrome-da 2 fərqli olmayan ünvanda təkrarlandı (screenshot var). Avtomatik test: UI-NAV-010</t>
   </si>
   <si>
-    <t xml:space="preserve">BUG-012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Naviqasiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kartlar menyusundan sonra Geri düyməsi ana səhifəyə qaytarmır</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. /az açın
-2. Menyudan Kartlar seçin (açılır /az/kartlar/debet)
-3. Brauzerin Geri düyməsini basın</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ana səhifə (/az) açılır</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avtomatlaşdırmada URL /az/kartlar/debet qaldı (yönləndirmə tələsi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rədd edildi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real Chrome-da əl ilə yoxlandı: Geri düyməsi /az-a qayıdır, bug yoxdur. Selenium nəticəsi avtomatlaşdırma artefaktı idi; UI-NAV-009 skriptdən çıxarıldı</t>
-  </si>
-  <si>
     <t xml:space="preserve">BUG-013</t>
   </si>
   <si>
@@ -547,71 +515,70 @@
     <t xml:space="preserve">Ən aşağı prioritet: kosmetik/texniki nüans, istifadəçi təcrübəsinə demək olar ki, təsir etmir (düzəliş sonraya saxlanıla bilər). Axtarışda "maks" tapılmır, kopyalanan mətn və ekran oxuyucu səhv işləyir. Avtomatik test: UI-LON-015. Digər yoxlanan 13 səhifədə belə hal yoxdur</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valyuta cədvəli</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nağd GBP və RUB məzənnə fərqi çox genişdir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Valyuta cədvəlinə baxın</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Məntiqli alış/satış fərqi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GBP 2.0000 / 2.2800; RUB 1.2000 / 2.0100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yoxlanmalıdır</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bug yox, müşahidədir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OBS-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xarici valyutadan AZN-ə çevirmədə Satış məzənnəsi istifadə olunur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Konvertorda USD → AZN seçin, 100 yazın</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spesifikasiyaya görə aydın qayda (bank alış məzənnəsi 1.6900)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100 USD → 170.00 AZN (Satış 1.7000). 100 RUB → 2.01 AZN (Satış 2.0100, Alış 1.2000)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maliyyə məlumatı olduğu üçün biznes ilə dəqiqləşməlidir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OBS-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filiallar və ATM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filiallar səhifəsində xəritə "Xəritə yüklənir..." mərhələsində qalır</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. /az/xidmet-shebekeleri/filiallar açın
-2. 10 saniyə gözləyin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xəritə və filial siyahısı yüklənir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real Chrome-da xəritə normal yüklənir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yalnız daxili brauzerdə baş vermişdi (mühit artefaktı), real Chrome-da yoxdur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OBS-004</t>
+    <t xml:space="preserve">BUG-024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Məbləğ sahəsi maksimum limiti (80 000) yoxlamır</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. /az açın
+2. Kalkulyatorda məbləğ sahəsinə 99999999 yazın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limit xətası və ya dəyərin 80 000-ə məhdudlaşdırılması</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sahə 99999999 qəbul edir, slayder 80000-də qalır (sinxron deyil), cəmi 101 822 141.21 AZN göstərilir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brauzerdə əl ilə təsdiqləndi (UI-CAL-018)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUG-025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ana səhifə</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Konsolda resurs və CORS xətaları</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. /az açın
+2. Brauzer konsoluna baxın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xəta yoxdur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORS (infobank.az), 404, 400, ERR_TOO_MANY_REDIRECTS və timeout xətaları</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bəzi timeout-lar test mühitindən ola bilər (UI-HOM-005)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUG-026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Əmanətlər</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Əmanət kalkulyatoru minimum məbləğdən (100) az dəyəri qəbul edir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. /az/emanetler/digital-depozit açın
+2. Məbləğ sahəsinə 99 yazın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xəta mesajı və ya rədd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99 qəbul edilir, 99.60 AZN cəmi göstərilir, xəta yoxdur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brauzerdə əl ilə təsdiqləndi (UI-DEP-018)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUG-027</t>
   </si>
   <si>
     <t xml:space="preserve">&lt; simvolu olan axtarış sorğusu WAF xam xəta səhifəsi göstərir</t>
@@ -626,10 +593,10 @@
     <t xml:space="preserve">"The requested URL was rejected" (Support ID ilə xam səhifə)</t>
   </si>
   <si>
-    <t xml:space="preserve">Təhlükəsizlik baxımından müsbətdir (XSS bloklanır), amma istifadəçi təcrübəsi pisdir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OBS-005</t>
+    <t xml:space="preserve">Təhlükəsizlik baxımından müsbətdir (XSS bloklanır), amma istifadəçiyə xam xəta göstərilir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUG-028</t>
   </si>
   <si>
     <t xml:space="preserve">Nəticəsiz axtarışda "tapılmadı" mesajı yoxdur</t>
@@ -647,51 +614,7 @@
     <t xml:space="preserve">UX təklifi</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Onlayn xidmətlər</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Footer və DostBank səhifəsindəki mobil tətbiq linkləri fərqlidir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. /az footer-dəki App Store və Huawei linklərinə baxın
-2. /az/onlayn-xidmetler/dostbank-mobil-bankciliq linklərinə baxın</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hər iki yerdə eyni tətbiq linki</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Footer: App Store id1444724229, Huawei C102554803. DostBank səhifəsi: App Store id1642869806, Huawei C109384997, Google Play com.bankofbaku.v2.dostbank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hansının aktual olduğunu biznes təsdiqləməlidir (köhnə və yeni tətbiq ola bilər)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OBS-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kartlar və Kreditlər</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kart və kredit detal ünvanları ardıcıl deyil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. /az/kartlar/debet və /az/kartlar/kredit-kartlari səhifələrində "Daha ətraflı" linklərinə baxın
-2. /az/kreditler/nagd-pul-krediti linklərinə baxın</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ardıcıl slug-əsaslı ünvanlar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bəzi kartlar rəqəmlə (/debet/113), bəziləri slug ilə (/digital-bolkart-debet); kredit kartlarının bir hissəsi /kartlar, bir hissəsi /kreditler altındadır; /nagd-pul-kreditleri/133 səhv ünvanı /nagd-pul-krediti/133-ə yönləndirilir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Funksional problem yoxdur, SEO və saxlanılabilirlik üçün qeyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OBS-008</t>
+    <t xml:space="preserve">BUG-029</t>
   </si>
   <si>
     <t xml:space="preserve">Kartlar</t>
@@ -713,47 +636,7 @@
     <t xml:space="preserve">Məzmun uyğunsuzluğu ola bilər, biznes təsdiqləməlidir</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Təhlükəsizlik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saytın ilk açılışında izləmə kukiləri razılıq soruşulmadan qurulur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Təmiz brauzerdə /az açın
-2. Kukilərə baxın</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Razılıq banneri və ya seçim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">_ga, _fbp, _ym_uid, _clck, _gcl_au, _tt_enable_cookie qurulur; banner görünmür</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yerli qanunvericiliyə və korporativ siyasətə uyğunluğu hüquq şöbəsi qiymətləndirməlidir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OBS-010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSP başlığı məhduddur, Permissions-Policy yoxdur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. /az sorğusunun cavab başlıqlarına baxın</t>
-  </si>
-  <si>
-    <t xml:space="preserve">script-src və s. direktivləri olan CSP, Permissions-Policy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Content-Security-Policy yalnız upgrade-insecure-requests və frame-ancestors ehtiva edir; HSTS, X-Frame-Options, nosniff, Referrer-Policy düzgündür</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Müsbət: server və X-Powered-By versiyaları açıqlanmır</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OBS-011</t>
+    <t xml:space="preserve">BUG-030</t>
   </si>
   <si>
     <t xml:space="preserve">Sitemap-dakı 13 ünvan yönləndirilir</t>
@@ -772,129 +655,7 @@
     <t xml:space="preserve">117 ünvan 200 qaytarır</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Çat və widget-lər</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Çat widget-i daxili brauzerdə görünmədi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. /az açın və 6 saniyə gözləyin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Çat düyməsi görünür</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOM-da çat elementi tapılmadı (__livechat_id kuki var)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real Chrome-da çat düyməsi görünür (istifadəçi yoxlayıb). Daxili brauzerdə görünməməsi test mühitinin məhdudiyyətidir, bug deyil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OBS-013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36 aydan böyük müddətdə (137) nəticə sahələri yox olur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. /az/emanetler/dinamik-emanet açın
-2. Müddət sahəsinə 137 daxil edin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xəta mesajı və ya minimum/maksimum dəyərə qaytarma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ümumi məbləğ və faiz sahələri yox olur, mesaj yoxdur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUG-019 ilə əlaqəli; Selenium diaqnostikası ilə tapılıb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OBS-014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sahə təmizləndikdə dəyər dərhal ilkin qiymətə qayıdır</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. /az/emanetler/dinamik-emanet açın
-2. Məbləğ sahəsini silin və rəqəm yazın</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yeni dəyər sahəyə yazılır</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sahə boşalan kimi 100 (müddətdə 1) qayıdır və yazılan rəqəm üstünə əlavə olunur (100 + 10000 = 10010000)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Selenium diaqnostikasında müşahidə olunub; əl ilə sildikdə də təkrarlanıb-təkrarlanmadığı yoxlanmalıdır</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUG-024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Məbləğ sahəsi maksimum limiti (80 000) yoxlamır</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. /az açın
-2. Kalkulyatorda məbləğ sahəsinə 99999999 yazın</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Limit xətası və ya dəyərin 80 000-ə məhdudlaşdırılması</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sahə 99999999 qəbul edir, slayder 80000-də qalır (sinxron deyil), cəmi 101 822 141.21 AZN göstərilir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brauzerdə əl ilə təsdiqləndi (UI-CAL-018)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUG-025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ana səhifə</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Konsolda resurs və CORS xətaları</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. /az açın
-2. Brauzer konsoluna baxın</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xəta yoxdur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORS (infobank.az), 404, 400, ERR_TOO_MANY_REDIRECTS və timeout xətaları</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bəzi timeout-lar test mühitindən ola bilər (UI-HOM-005)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUG-026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Əmanətlər</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Əmanət kalkulyatoru minimum məbləğdən (100) az dəyəri qəbul edir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. /az/emanetler/digital-depozit açın
-2. Məbləğ sahəsinə 99 yazın</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Xəta mesajı və ya rədd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99 qəbul edilir, 99.60 AZN cəmi göstərilir, xəta yoxdur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brauzerdə əl ilə təsdiqləndi (UI-DEP-018)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OBS-015</t>
+    <t xml:space="preserve">BUG-031</t>
   </si>
   <si>
     <t xml:space="preserve">Kampaniyalar</t>
@@ -916,7 +677,7 @@
     <t xml:space="preserve">Biznes ilə dəqiqləşdirmək (UI-CMP-002)</t>
   </si>
   <si>
-    <t xml:space="preserve">OBS-016</t>
+    <t xml:space="preserve">BUG-032</t>
   </si>
   <si>
     <t xml:space="preserve">SEO və dillər</t>
@@ -950,7 +711,7 @@
     <t xml:space="preserve">Addım</t>
   </si>
   <si>
-    <t xml:space="preserve">Çat widget-i real Chrome-da yoxlandı, görünür (OBS-012 rədd edildi)</t>
+    <t xml:space="preserve">Çat widget-i real Chrome-da yoxlandı, görünür</t>
   </si>
   <si>
     <t xml:space="preserve">UI-CHT-001 və 005 əl ilə yoxlandı, keçdi</t>
@@ -965,7 +726,7 @@
     <t xml:space="preserve">Bug-ların biznesə təqdimi</t>
   </si>
   <si>
-    <t xml:space="preserve">BUG-017 – 026 və OBS-006 – 016 üçün biznes təsdiqi lazımdır</t>
+    <t xml:space="preserve">BUG-017 – 032 üçün biznes təsdiqi lazımdır</t>
   </si>
   <si>
     <t xml:space="preserve">Avtomatlaşdırma</t>
@@ -1260,9 +1021,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>182160</xdr:colOff>
+      <xdr:colOff>181800</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>16560</xdr:rowOff>
+      <xdr:rowOff>16200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1276,7 +1037,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="571680"/>
-          <a:ext cx="10474920" cy="6302880"/>
+          <a:ext cx="10474560" cy="6302520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1297,9 +1058,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>182160</xdr:colOff>
+      <xdr:colOff>181800</xdr:colOff>
       <xdr:row>73</xdr:row>
-      <xdr:rowOff>16560</xdr:rowOff>
+      <xdr:rowOff>16200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1313,7 +1074,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="7620120"/>
-          <a:ext cx="10474920" cy="6302880"/>
+          <a:ext cx="10474560" cy="6302520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1661,117 +1422,117 @@
         <v>15</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="G7" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>15</v>
@@ -1780,56 +1541,56 @@
         <v>16</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="G10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>15</v>
@@ -1838,27 +1599,27 @@
         <v>16</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>15</v>
@@ -1867,56 +1628,56 @@
         <v>16</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="F13" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>15</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>15</v>
@@ -1925,27 +1686,27 @@
         <v>16</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="F15" s="3" t="s">
         <v>99</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>15</v>
@@ -1954,114 +1715,114 @@
         <v>16</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="F16" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="G17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="G18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>120</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="F19" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>129</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>15</v>
@@ -2070,710 +1831,512 @@
         <v>16</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="G20" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="F21" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="G21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="G22" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="F23" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="G24" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="F25" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="G25" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C26" s="3" t="s">
+      <c r="G26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="G27" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>180</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="G29" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="G30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="G31" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>206</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="G32" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>218</v>
-      </c>
     </row>
     <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>225</v>
-      </c>
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>231</v>
-      </c>
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>237</v>
-      </c>
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>244</v>
-      </c>
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>250</v>
-      </c>
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>256</v>
-      </c>
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>262</v>
-      </c>
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
     </row>
     <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>269</v>
-      </c>
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
     </row>
     <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>276</v>
-      </c>
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
     </row>
     <row r="42" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>283</v>
-      </c>
+      <c r="A42" s="3"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
     </row>
     <row r="43" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>290</v>
-      </c>
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I15"/>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H2:H200" type="list">
-      <formula1>"Yeni,Yoxlanmalıdır,Təsdiqləndi,Düzəldildi,Rədd edildi"</formula1>
+      <formula1>"Yeni,Təsdiqləndi,Düzəldildi"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G2:G200" type="list">
@@ -2808,7 +2371,7 @@
         <v>6</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>291</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2816,7 +2379,7 @@
         <v>29</v>
       </c>
       <c r="B2" s="5" t="n">
-        <f aca="false">COUNTIFS('Bug siyahısı'!G2:G200,A2,'Bug siyahısı'!H2:H200,"&lt;&gt;Rədd edildi")</f>
+        <f aca="false">COUNTIF('Bug siyahısı'!G2:G200,A2)</f>
         <v>1</v>
       </c>
     </row>
@@ -2825,26 +2388,26 @@
         <v>15</v>
       </c>
       <c r="B3" s="5" t="n">
-        <f aca="false">COUNTIFS('Bug siyahısı'!G2:G200,A3,'Bug siyahısı'!H2:H200,"&lt;&gt;Rədd edildi")</f>
-        <v>14</v>
+        <f aca="false">COUNTIF('Bug siyahısı'!G2:G200,A3)</f>
+        <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" s="5" t="n">
-        <f aca="false">COUNTIFS('Bug siyahısı'!G2:G200,A4,'Bug siyahısı'!H2:H200,"&lt;&gt;Rədd edildi")</f>
-        <v>24</v>
+        <f aca="false">COUNTIF('Bug siyahısı'!G2:G200,A4)</f>
+        <v>17</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>292</v>
+        <v>215</v>
       </c>
       <c r="B5" s="6" t="n">
         <f aca="false">SUM(B2:B4)</f>
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -2873,10 +2436,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>293</v>
+        <v>216</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>294</v>
+        <v>217</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>8</v>
@@ -2887,10 +2450,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>295</v>
+        <v>218</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>296</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2898,10 +2461,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>297</v>
+        <v>220</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>298</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2909,10 +2472,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>299</v>
+        <v>222</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>300</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2920,10 +2483,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>301</v>
+        <v>224</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>302</v>
+        <v>225</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2931,10 +2494,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>303</v>
+        <v>226</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>304</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -2963,17 +2526,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>305</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>306</v>
+        <v>229</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>307</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Final_Project_UI_Bug_Siyahisi.xlsx
+++ b/docs/Final_Project_UI_Bug_Siyahisi.xlsx
@@ -720,7 +720,7 @@
     <t xml:space="preserve">Qalan yoxlamalar</t>
   </si>
   <si>
-    <t xml:space="preserve">Qalan 21 case: hücum xarakterli (ERR-003, SRC-004, SEC-005), offline (ERR-004), kontrast/fokus (A11-002, 005), performans (PRF-001), dil qaydaları (LNG-005…012), NAV-013, HOM-002, CAL-017, 019, 020, CHT-004</t>
+    <t xml:space="preserve">Qalan 15 case: hücum xarakterli (ERR-003, SRC-004, SEC-005), kontrast/fokus (A11-002, 005), performans (PRF-001), LNG-007, 011, 012, NAV-013, HOM-002, CAL-017, 019, 020, CHT-004</t>
   </si>
   <si>
     <t xml:space="preserve">Bug-ların biznesə təqdimi</t>
@@ -1021,9 +1021,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>181800</xdr:colOff>
+      <xdr:colOff>181080</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>16200</xdr:rowOff>
+      <xdr:rowOff>15480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1037,7 +1037,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="571680"/>
-          <a:ext cx="10474560" cy="6302520"/>
+          <a:ext cx="10473840" cy="6301800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1058,9 +1058,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>181800</xdr:colOff>
+      <xdr:colOff>181080</xdr:colOff>
       <xdr:row>73</xdr:row>
-      <xdr:rowOff>16200</xdr:rowOff>
+      <xdr:rowOff>15480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1074,7 +1074,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="7620120"/>
-          <a:ext cx="10474560" cy="6302520"/>
+          <a:ext cx="10473840" cy="6301800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/docs/Final_Project_UI_Bug_Siyahisi.xlsx
+++ b/docs/Final_Project_UI_Bug_Siyahisi.xlsx
@@ -204,7 +204,7 @@
     <t xml:space="preserve">Dil</t>
   </si>
   <si>
-    <t xml:space="preserve">/en səhifəsində html lang atributu "az" qalır</t>
+    <t xml:space="preserve">/en və /ru səhifələrində html lang atributu "az" qalır</t>
   </si>
   <si>
     <t xml:space="preserve">1. https://www.bankofbaku.com/en açın
@@ -217,13 +217,13 @@
     <t xml:space="preserve">lang="az"</t>
   </si>
   <si>
-    <t xml:space="preserve">Ekran oxuyucular və SEO üçün səhv dil; avtomatik test ilə təsdiqləndi</t>
+    <t xml:space="preserve">Ekran oxuyucular və SEO üçün səhv dil; avtomatik test ilə təsdiqləndi; /ru üçün də 12.10.2026 əl ilə təsdiqləndi</t>
   </si>
   <si>
     <t xml:space="preserve">BUG-009</t>
   </si>
   <si>
-    <t xml:space="preserve">/en səhifəsinin başlığı (title) Azərbaycan dilindədir</t>
+    <t xml:space="preserve">/en və /ru səhifələrinin başlığı (title) Azərbaycan dilindədir</t>
   </si>
   <si>
     <t xml:space="preserve">1. /en açın
@@ -236,7 +236,7 @@
     <t xml:space="preserve">"Bank of Baku - Sizə yaxın bankçılıq!"</t>
   </si>
   <si>
-    <t xml:space="preserve">SEO və istifadəçi təcrübəsi; avtomatik test ilə təsdiqləndi</t>
+    <t xml:space="preserve">SEO və istifadəçi təcrübəsi; avtomatik test ilə təsdiqləndi; /ru üçün də 12.10.2026 əl ilə təsdiqləndi</t>
   </si>
   <si>
     <t xml:space="preserve">BUG-010</t>
@@ -683,20 +683,20 @@
     <t xml:space="preserve">SEO və dillər</t>
   </si>
   <si>
-    <t xml:space="preserve">/en və /ru səhifələrində html lang="az", başlıq AZ; daxili səhifələrdə canonical /az-a işarə edir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. /en və /ru açın, html lang və title-a baxın
-2. /az/kartlar/debet canonical-a baxın</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lang="en"/"ru", müvafiq başlıq; canonical öz URL-ni göstərir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lang="az" və AZ başlıq; canonical https://www.bankofbaku.com/az; /az/biznes başlığı ana səhifə başlığıdır</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UI-LNG-003, 004, ERR-002, BIZ-002</t>
+    <t xml:space="preserve">Daxili səhifələrdə canonical linki həmişə /az ana səhifəsinə işarə edir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. /az/kartlar/debet açın
+2. Səhifə mənbəyində &lt;link rel="canonical"&gt; dəyərinə baxın</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canonical səhifənin öz ünvanını göstərməlidir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical = https://www.bankofbaku.com/az (daxili səhifə üçün də)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axtarış sistemləri daxili səhifələri ana səhifənin təkrarı kimi görə bilər (UI-ERR-002)</t>
   </si>
   <si>
     <t xml:space="preserve">Say</t>
@@ -1021,9 +1021,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>181080</xdr:colOff>
+      <xdr:colOff>180720</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>15480</xdr:rowOff>
+      <xdr:rowOff>15120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1037,7 +1037,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="571680"/>
-          <a:ext cx="10473840" cy="6301800"/>
+          <a:ext cx="10473480" cy="6301440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1058,9 +1058,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>181080</xdr:colOff>
+      <xdr:colOff>180720</xdr:colOff>
       <xdr:row>73</xdr:row>
-      <xdr:rowOff>15480</xdr:rowOff>
+      <xdr:rowOff>15120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1074,7 +1074,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="7620120"/>
-          <a:ext cx="10473840" cy="6301800"/>
+          <a:ext cx="10473480" cy="6301440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/docs/Final_Project_UI_Bug_Siyahisi.xlsx
+++ b/docs/Final_Project_UI_Bug_Siyahisi.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="198">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -578,64 +578,6 @@
     <t xml:space="preserve">Brauzerdə əl ilə təsdiqləndi (UI-DEP-018)</t>
   </si>
   <si>
-    <t xml:space="preserve">BUG-027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt; simvolu olan axtarış sorğusu WAF xam xəta səhifəsi göstərir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. /az/axtar?q=&lt;img src=x onerror=alert(1)&gt; açın</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sorğu mətn kimi göstərilir və ya dostane xəta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"The requested URL was rejected" (Support ID ilə xam səhifə)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Təhlükəsizlik baxımından müsbətdir (XSS bloklanır), amma istifadəçiyə xam xəta göstərilir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUG-028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nəticəsiz axtarışda "tapılmadı" mesajı yoxdur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. /az/axtar?q=zzzxqw123 açın</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Nəticə tapılmadı" mesajı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yalnız "0 Nəticə" və boş pagination göstərilir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UX təklifi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUG-029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kartlar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debet kart siyahısında bəzi kartların qiyməti göstərilmir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. /az/kartlar/debet açın
-2. Bolkart Platinum debet və Maaş kartı bloklarına baxın</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bütün kartlarda eyni sahələr (qiymət, müddət)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platinum və Maaş kartında "Kartın qiyməti" yoxdur, Digital Bolkartda "İllik faiz" göstərilir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Məzmun uyğunsuzluğu ola bilər, biznes təsdiqləməlidir</t>
-  </si>
-  <si>
     <t xml:space="preserve">BUG-030</t>
   </si>
   <si>
@@ -655,50 +597,6 @@
     <t xml:space="preserve">117 ünvan 200 qaytarır</t>
   </si>
   <si>
-    <t xml:space="preserve">BUG-031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kampaniyalar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vaxtı bitmiş müsabiqə hələ də siyahıdadır</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. /az/kampaniyalar açın
-2. "İstanbula 2 nəfərlik bilet" kampaniyasına baxın</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bitmiş kampaniya aktiv kimi görünmür</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Müsabiqə 17–27 iyul 2026 üçün idi, oktyabrda hələ siyahıdadır</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Biznes ilə dəqiqləşdirmək (UI-CMP-002)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BUG-032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEO və dillər</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Daxili səhifələrdə canonical linki həmişə /az ana səhifəsinə işarə edir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. /az/kartlar/debet açın
-2. Səhifə mənbəyində &lt;link rel="canonical"&gt; dəyərinə baxın</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canonical səhifənin öz ünvanını göstərməlidir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical = https://www.bankofbaku.com/az (daxili səhifə üçün də)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axtarış sistemləri daxili səhifələri ana səhifənin təkrarı kimi görə bilər (UI-ERR-002)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Say</t>
   </si>
   <si>
@@ -726,7 +624,7 @@
     <t xml:space="preserve">Bug-ların biznesə təqdimi</t>
   </si>
   <si>
-    <t xml:space="preserve">BUG-017 – 032 üçün biznes təsdiqi lazımdır</t>
+    <t xml:space="preserve">BUG-017 – 026 və BUG-030 üçün biznes təsdiqi lazımdır</t>
   </si>
   <si>
     <t xml:space="preserve">Avtomatlaşdırma</t>
@@ -1021,9 +919,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>180720</xdr:colOff>
+      <xdr:colOff>180360</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>15120</xdr:rowOff>
+      <xdr:rowOff>14760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1037,7 +935,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="571680"/>
-          <a:ext cx="10473480" cy="6301440"/>
+          <a:ext cx="10473120" cy="6301080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1058,9 +956,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>180720</xdr:colOff>
+      <xdr:colOff>180360</xdr:colOff>
       <xdr:row>73</xdr:row>
-      <xdr:rowOff>15120</xdr:rowOff>
+      <xdr:rowOff>14760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1074,7 +972,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="7620120"/>
-          <a:ext cx="10473480" cy="6301440"/>
+          <a:ext cx="10473120" cy="6301080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2042,7 +1940,7 @@
         <v>175</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>176</v>
@@ -2067,149 +1965,59 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>186</v>
-      </c>
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
     </row>
     <row r="29" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>193</v>
-      </c>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
     </row>
     <row r="30" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>199</v>
-      </c>
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
     </row>
     <row r="31" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>206</v>
-      </c>
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
     </row>
     <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>213</v>
-      </c>
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
     </row>
     <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3"/>
@@ -2371,7 +2179,7 @@
         <v>6</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>214</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2398,16 +2206,16 @@
       </c>
       <c r="B4" s="5" t="n">
         <f aca="false">COUNTIF('Bug siyahısı'!G2:G200,A4)</f>
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>215</v>
+        <v>182</v>
       </c>
       <c r="B5" s="6" t="n">
         <f aca="false">SUM(B2:B4)</f>
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -2436,10 +2244,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>216</v>
+        <v>183</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>217</v>
+        <v>184</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>8</v>
@@ -2450,10 +2258,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>218</v>
+        <v>185</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2461,10 +2269,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>221</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2472,10 +2280,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2483,10 +2291,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>224</v>
+        <v>191</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>225</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2494,10 +2302,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>226</v>
+        <v>193</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>227</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -2526,17 +2334,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>229</v>
+        <v>196</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
